--- a/data.mn/public/datasets/sown-area-by-crop-type.xlsx
+++ b/data.mn/public/datasets/sown-area-by-crop-type.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,505 +414,1235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Crop Type</t>
+          <t>year</t>
         </is>
       </c>
-      <c r="B1" t="n">
-        <v>1978</v>
-      </c>
-      <c r="C1" t="n">
-        <v>1979</v>
-      </c>
-      <c r="D1" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E1" t="n">
-        <v>1981</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1982</v>
-      </c>
-      <c r="G1" t="n">
-        <v>1983</v>
-      </c>
-      <c r="H1" t="n">
-        <v>1984</v>
-      </c>
-      <c r="I1" t="n">
-        <v>1985</v>
-      </c>
-      <c r="J1" t="n">
-        <v>1986</v>
-      </c>
-      <c r="K1" t="n">
-        <v>1987</v>
-      </c>
-      <c r="L1" t="n">
-        <v>1988</v>
-      </c>
-      <c r="M1" t="n">
-        <v>1989</v>
-      </c>
-      <c r="N1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="O1" t="n">
-        <v>1991</v>
-      </c>
-      <c r="P1" t="n">
-        <v>1992</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>2014</v>
-      </c>
-      <c r="R1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="S1" t="n">
-        <v>2016</v>
-      </c>
-      <c r="T1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="U1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="V1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="W1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Z1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AA1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AB1" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cereals</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>569.9</v>
-      </c>
-      <c r="C2" t="n">
-        <v>585.5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>557.5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>542.3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>529.1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>586.6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>619.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>636.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>629.7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>622.9</v>
-      </c>
-      <c r="L2" t="n">
-        <v>641.6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>673.4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>654.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>615.3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>592.6</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>315.03</v>
-      </c>
-      <c r="R2" t="n">
-        <v>390.69</v>
-      </c>
-      <c r="S2" t="n">
-        <v>377.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>390.86</v>
-      </c>
-      <c r="U2" t="n">
-        <v>366.81</v>
-      </c>
-      <c r="V2" t="n">
-        <v>369.45</v>
-      </c>
-      <c r="W2" t="n">
-        <v>408.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>432.75</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>385.06</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>363.06</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>354.36</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>310.87</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Fodder crops</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>102.6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>102.1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>136.7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>133.8</v>
-      </c>
-      <c r="F3" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>124.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>139.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>159</v>
-      </c>
-      <c r="K3" t="n">
-        <v>160.8</v>
-      </c>
-      <c r="L3" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>147.7</v>
-      </c>
-      <c r="N3" t="n">
-        <v>117.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="P3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="R3" t="n">
-        <v>23.84</v>
-      </c>
-      <c r="S3" t="n">
-        <v>29.89</v>
-      </c>
-      <c r="T3" t="n">
-        <v>26.22</v>
-      </c>
-      <c r="U3" t="n">
-        <v>46.31</v>
-      </c>
-      <c r="V3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>84.54000000000001</v>
-      </c>
-      <c r="X3" t="n">
-        <v>108.34</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>106.93</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>100.81</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>93.36</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Industrial crops</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>86.68000000000001</v>
-      </c>
-      <c r="R4" t="n">
-        <v>84.45999999999999</v>
-      </c>
-      <c r="S4" t="n">
-        <v>66.18000000000001</v>
-      </c>
-      <c r="T4" t="n">
-        <v>81.01000000000001</v>
-      </c>
-      <c r="U4" t="n">
-        <v>71.95</v>
-      </c>
-      <c r="V4" t="n">
-        <v>86.18000000000001</v>
-      </c>
-      <c r="W4" t="n">
-        <v>64.64</v>
-      </c>
-      <c r="X4" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>124.11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>136.91</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>132.39</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>154.79</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Potatoes</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="S5" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="T5" t="n">
-        <v>15.15</v>
-      </c>
-      <c r="U5" t="n">
-        <v>12.92</v>
-      </c>
-      <c r="V5" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>19.42</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>13.39</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Vegetables</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B2" t="n">
+        <v>569.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B3" t="n">
+        <v>585.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B4" t="n">
+        <v>557.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>136.7</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B5" t="n">
+        <v>542.3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1982</v>
+      </c>
       <c r="B6" t="n">
+        <v>529.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B7" t="n">
+        <v>586.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B8" t="n">
+        <v>619.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B9" t="n">
+        <v>636.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B10" t="n">
+        <v>629.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>159</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B11" t="n">
+        <v>622.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>160.8</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B12" t="n">
+        <v>641.6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B13" t="n">
+        <v>673.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B14" t="n">
+        <v>654.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B15" t="n">
+        <v>615.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B16" t="n">
+        <v>592.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B17" t="n">
+        <v>315.03</v>
+      </c>
+      <c r="C17" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="D17" t="n">
+        <v>86.68000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B18" t="n">
+        <v>390.69</v>
+      </c>
+      <c r="C18" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="D18" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B19" t="n">
+        <v>377.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="D19" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B20" t="n">
+        <v>390.86</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="D20" t="n">
+        <v>81.01000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F20" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.359999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B21" t="n">
+        <v>366.81</v>
+      </c>
+      <c r="C21" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="D21" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.869999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B22" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="C22" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B23" t="n">
+        <v>408.07</v>
+      </c>
+      <c r="C23" t="n">
+        <v>84.54000000000001</v>
+      </c>
+      <c r="D23" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10.57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B24" t="n">
+        <v>432.75</v>
+      </c>
+      <c r="C24" t="n">
+        <v>108.34</v>
+      </c>
+      <c r="D24" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11.22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B25" t="n">
+        <v>385.06</v>
+      </c>
+      <c r="C25" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>124.11</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F25" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14.21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B26" t="n">
+        <v>363.06</v>
+      </c>
+      <c r="C26" t="n">
+        <v>106.93</v>
+      </c>
+      <c r="D26" t="n">
+        <v>136.91</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15.79</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B27" t="n">
+        <v>354.36</v>
+      </c>
+      <c r="C27" t="n">
+        <v>100.81</v>
+      </c>
+      <c r="D27" t="n">
+        <v>132.39</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="F27" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20.23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B28" t="n">
+        <v>310.87</v>
+      </c>
+      <c r="C28" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="D28" t="n">
+        <v>154.79</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="F28" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Бусад</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Техникийн ургамал</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Тэжээлийн ургамал</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Төмс</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Хүнсний ногоо</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Үр тариа</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F2" t="n">
         <v>6.6</v>
       </c>
-      <c r="C6" t="n">
+      <c r="G2" t="n">
+        <v>569.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F3" t="n">
         <v>2.4</v>
       </c>
+      <c r="G3" t="n">
+        <v>585.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>136.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>557.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>542.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>9.800000000000001</v>
+        <v>102.9</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="n">
+        <v>529.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F7" t="n">
         <v>2.8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="G7" t="n">
+        <v>586.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F8" t="n">
         <v>2.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="G8" t="n">
+        <v>619.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F9" t="n">
         <v>3.3</v>
       </c>
-      <c r="J6" t="n">
+      <c r="G9" t="n">
+        <v>636.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>159</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F10" t="n">
         <v>3.8</v>
       </c>
-      <c r="K6" t="n">
+      <c r="G10" t="n">
+        <v>629.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>160.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F11" t="n">
         <v>4</v>
       </c>
-      <c r="L6" t="n">
+      <c r="G11" t="n">
+        <v>622.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F12" t="n">
         <v>4.1</v>
       </c>
-      <c r="M6" t="n">
+      <c r="G12" t="n">
+        <v>641.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F13" t="n">
         <v>4.2</v>
       </c>
-      <c r="N6" t="n">
+      <c r="G13" t="n">
+        <v>673.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F14" t="n">
         <v>3.6</v>
       </c>
-      <c r="O6" t="n">
+      <c r="G14" t="n">
+        <v>654.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F15" t="n">
         <v>2.8</v>
       </c>
-      <c r="P6" t="n">
+      <c r="G15" t="n">
+        <v>615.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F16" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="G16" t="n">
+        <v>592.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C17" t="n">
+        <v>86.68000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="E17" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F17" t="n">
         <v>8.66</v>
       </c>
-      <c r="R6" t="n">
+      <c r="G17" t="n">
+        <v>315.03</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="C18" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F18" t="n">
         <v>7.65</v>
       </c>
-      <c r="S6" t="n">
+      <c r="G18" t="n">
+        <v>390.69</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="E19" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="F19" t="n">
         <v>8.9</v>
       </c>
-      <c r="T6" t="n">
+      <c r="G19" t="n">
+        <v>377.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C20" t="n">
+        <v>81.01000000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="E20" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="F20" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="U6" t="n">
+      <c r="G20" t="n">
+        <v>390.86</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C21" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="D21" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="F21" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="V6" t="n">
+      <c r="G21" t="n">
+        <v>366.81</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C22" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="F22" t="n">
         <v>8.44</v>
       </c>
-      <c r="W6" t="n">
+      <c r="G22" t="n">
+        <v>369.45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="D23" t="n">
+        <v>84.54000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="F23" t="n">
         <v>10.57</v>
       </c>
-      <c r="X6" t="n">
+      <c r="G23" t="n">
+        <v>408.07</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="D24" t="n">
+        <v>108.34</v>
+      </c>
+      <c r="E24" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="F24" t="n">
         <v>11.22</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="G24" t="n">
+        <v>432.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C25" t="n">
+        <v>124.11</v>
+      </c>
+      <c r="D25" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="F25" t="n">
         <v>14.21</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="G25" t="n">
+        <v>385.06</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>136.91</v>
+      </c>
+      <c r="D26" t="n">
+        <v>106.93</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="F26" t="n">
         <v>15.79</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="G26" t="n">
+        <v>363.06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="C27" t="n">
+        <v>132.39</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100.81</v>
+      </c>
+      <c r="E27" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="F27" t="n">
         <v>20.23</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="G27" t="n">
+        <v>354.36</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="C28" t="n">
+        <v>154.79</v>
+      </c>
+      <c r="D28" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="F28" t="n">
         <v>16.33</v>
+      </c>
+      <c r="G28" t="n">
+        <v>310.87</v>
       </c>
     </row>
   </sheetData>
